--- a/reconciliation-contenu-teleexpertise/ig/StructureDefinition-url-ltle.xlsx
+++ b/reconciliation-contenu-teleexpertise/ig/StructureDefinition-url-ltle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:58:57+00:00</t>
+    <t>2026-07-24T15:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
